--- a/Java25 TranVanThanhDatabase Design.xlsx
+++ b/Java25 TranVanThanhDatabase Design.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - plan and doc\Phần 3 - Database(MySQL)\16. RBDMS\DEMO\RDBMS demo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JAVA\java25\3. Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4387BC7E-9F9D-4AE6-8B47-86972CA1DD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="21600" windowHeight="12645" tabRatio="588" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="21600" windowHeight="12648" tabRatio="588" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Mô hình quan niệm" sheetId="1" r:id="rId1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="263">
   <si>
     <t>MatHang</t>
   </si>
@@ -358,9 +357,6 @@
   </si>
   <si>
     <t>Disable constraint FK …..</t>
-  </si>
-  <si>
-    <t>1. Xác định các đối tượng và thông tin cần lưu trữ</t>
   </si>
   <si>
     <r>
@@ -837,12 +833,117 @@
   <si>
     <t>Trigger, View</t>
   </si>
+  <si>
+    <t>CaLamViec</t>
+  </si>
+  <si>
+    <t>LoaiHang</t>
+  </si>
+  <si>
+    <t>NhaSanXuat</t>
+  </si>
+  <si>
+    <t>CungCapMatHang</t>
+  </si>
+  <si>
+    <t>MaNV</t>
+  </si>
+  <si>
+    <t>MaCLV</t>
+  </si>
+  <si>
+    <t>MaNSX</t>
+  </si>
+  <si>
+    <t>MaTTDH</t>
+  </si>
+  <si>
+    <t>TenNV</t>
+  </si>
+  <si>
+    <t>ThoiGianBatDau</t>
+  </si>
+  <si>
+    <t>TenLH</t>
+  </si>
+  <si>
+    <t>TenNSX</t>
+  </si>
+  <si>
+    <t>DanhSachMatHang</t>
+  </si>
+  <si>
+    <t>HoTen</t>
+  </si>
+  <si>
+    <t>NgayTaoHD</t>
+  </si>
+  <si>
+    <t>Mô tả</t>
+  </si>
+  <si>
+    <t>ThoiGianKetThuc</t>
+  </si>
+  <si>
+    <t>DiaChi</t>
+  </si>
+  <si>
+    <t>SDT</t>
+  </si>
+  <si>
+    <t>NhanVienPhuTrach</t>
+  </si>
+  <si>
+    <t>ThuMay</t>
+  </si>
+  <si>
+    <t>MauSac</t>
+  </si>
+  <si>
+    <t>NgayTaoDonHang</t>
+  </si>
+  <si>
+    <t>SoTienConLaiPhaiTT</t>
+  </si>
+  <si>
+    <t>ThoiGianCungCap</t>
+  </si>
+  <si>
+    <t>LoaiHinhThanhToan</t>
+  </si>
+  <si>
+    <t>TaiKhoan</t>
+  </si>
+  <si>
+    <t>SoLuongConLai</t>
+  </si>
+  <si>
+    <t>TongTien</t>
+  </si>
+  <si>
+    <t>MatKhau</t>
+  </si>
+  <si>
+    <t>PhiVanChuyen</t>
+  </si>
+  <si>
+    <t>ChatLieu</t>
+  </si>
+  <si>
+    <t>1. Mô hình quan niệm</t>
+  </si>
+  <si>
+    <t>A. Xác định các đối tượng cần lưu trữ</t>
+  </si>
+  <si>
+    <t>B. Xác định các thuộc tính của đối tượng</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -928,6 +1029,27 @@
     <font>
       <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Corbel"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1048,7 +1170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1091,12 +1213,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1187,6 +1303,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1533,232 +1681,555 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:K24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" customWidth="1"/>
-    <col min="10" max="20" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" customWidth="1"/>
+    <col min="7" max="7" width="18.77734375" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" customWidth="1"/>
+    <col min="9" max="9" width="23.33203125" customWidth="1"/>
+    <col min="10" max="10" width="29.77734375" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" customWidth="1"/>
+    <col min="12" max="14" width="18.77734375" customWidth="1"/>
+    <col min="15" max="23" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="24" spans="2:11" s="18" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="58"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+    </row>
+    <row r="2" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+    </row>
+    <row r="3" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52"/>
+    </row>
+    <row r="4" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="55" t="s">
+        <v>234</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="J4" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="55" t="s">
+        <v>230</v>
+      </c>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+    </row>
+    <row r="5" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>240</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>241</v>
+      </c>
+      <c r="H5" s="55" t="s">
+        <v>242</v>
+      </c>
+      <c r="I5" s="55" t="s">
+        <v>243</v>
+      </c>
+      <c r="J5" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
+    </row>
+    <row r="6" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="55" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55" t="s">
+        <v>247</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="52"/>
+    </row>
+    <row r="7" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="55"/>
+      <c r="B7" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="E7" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="F7" s="55" t="s">
+        <v>250</v>
+      </c>
+      <c r="G7" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="H7" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
+    </row>
+    <row r="8" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="55"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="56" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" s="55" t="s">
+        <v>254</v>
+      </c>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="52"/>
+    </row>
+    <row r="9" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="55"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55" t="s">
+        <v>256</v>
+      </c>
+      <c r="G9" s="55" t="s">
+        <v>257</v>
+      </c>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52"/>
+    </row>
+    <row r="10" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="55"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55" t="s">
+        <v>258</v>
+      </c>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="52"/>
+      <c r="O10" s="52"/>
+      <c r="P10" s="52"/>
+    </row>
+    <row r="11" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="55"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="55"/>
+      <c r="F11" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="52"/>
+      <c r="P11" s="52"/>
+    </row>
+    <row r="12" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55" t="s">
+        <v>259</v>
+      </c>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="52"/>
+      <c r="P12" s="52"/>
+    </row>
+    <row r="13" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="52"/>
+      <c r="P13" s="52"/>
+    </row>
+    <row r="14" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="55"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
+      <c r="P14" s="52"/>
+    </row>
+    <row r="15" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="55"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="52"/>
+      <c r="P15" s="52"/>
+    </row>
+    <row r="16" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="57"/>
+      <c r="B16" s="59" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
+      <c r="P16" s="52"/>
+    </row>
+    <row r="17" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="57"/>
+      <c r="B17" s="59" t="s">
+        <v>261</v>
+      </c>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
+      <c r="P17" s="52"/>
+    </row>
+    <row r="18" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="57"/>
+      <c r="B18" s="59" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="52"/>
+      <c r="P18" s="52"/>
+    </row>
+    <row r="19" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="57"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="52"/>
+      <c r="O19" s="52"/>
+      <c r="P19" s="52"/>
+    </row>
+    <row r="20" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="57"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="52"/>
+      <c r="O20" s="52"/>
+      <c r="P20" s="52"/>
+    </row>
+    <row r="21" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="52"/>
+      <c r="P21" s="52"/>
+    </row>
+    <row r="22" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="63"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="63"/>
+      <c r="K22" s="63"/>
+    </row>
+    <row r="23" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -1766,51 +2237,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:U43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" customWidth="1"/>
-    <col min="16" max="16" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L2" t="s">
-        <v>225</v>
-      </c>
-      <c r="M2" s="51"/>
-      <c r="N2" s="24"/>
+        <v>224</v>
+      </c>
+      <c r="M2" s="49"/>
+      <c r="N2" s="22"/>
       <c r="O2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>82</v>
       </c>
-      <c r="P4" s="52"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="N5" s="52"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="P4" s="50"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="N5" s="50"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
         <v>43</v>
       </c>
@@ -1822,16 +2293,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D8" s="5"/>
-      <c r="P8" s="25" t="s">
+      <c r="P8" s="23" t="s">
         <v>59</v>
       </c>
       <c r="Q8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>28</v>
       </c>
@@ -1850,7 +2321,7 @@
       <c r="I9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="26" t="s">
+      <c r="J9" s="24" t="s">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="s">
@@ -1862,17 +2333,17 @@
       <c r="N9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="26" t="s">
+      <c r="O9" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="25" t="s">
+      <c r="P9" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="Q9" s="23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q9" s="21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>45</v>
       </c>
@@ -1891,7 +2362,7 @@
       <c r="I10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="26" t="s">
+      <c r="J10" s="24" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="4" t="s">
@@ -1903,17 +2374,17 @@
       <c r="N10" s="4">
         <v>20</v>
       </c>
-      <c r="O10" s="26" t="s">
+      <c r="O10" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="P10" s="27" t="s">
+      <c r="P10" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="Q10" s="28" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q10" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>63</v>
       </c>
@@ -1932,7 +2403,7 @@
       <c r="I11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="26" t="s">
+      <c r="J11" s="24" t="s">
         <v>24</v>
       </c>
       <c r="L11" s="4" t="s">
@@ -1944,11 +2415,11 @@
       <c r="N11" s="4">
         <v>30</v>
       </c>
-      <c r="O11" s="26" t="s">
+      <c r="O11" s="24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>46</v>
       </c>
@@ -1967,7 +2438,7 @@
       <c r="I12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="26" t="s">
+      <c r="J12" s="24" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="4" t="s">
@@ -1979,11 +2450,11 @@
       <c r="N12" s="4">
         <v>60</v>
       </c>
-      <c r="O12" s="26" t="s">
+      <c r="O12" s="24" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>57</v>
       </c>
@@ -1999,14 +2470,14 @@
       <c r="Q13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="R13" s="54" t="s">
+      <c r="R13" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="54"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="S13" s="64"/>
+      <c r="T13" s="64"/>
+      <c r="U13" s="64"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D14" s="5"/>
       <c r="O14" s="13" t="s">
         <v>43</v>
@@ -2017,20 +2488,20 @@
       <c r="Q14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="R14" s="54"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="54"/>
-      <c r="U14" s="54"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="R14" s="64"/>
+      <c r="S14" s="64"/>
+      <c r="T14" s="64"/>
+      <c r="U14" s="64"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="J16" s="52"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="J16" s="50"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="11" t="s">
         <v>37</v>
       </c>
@@ -2047,10 +2518,10 @@
         <v>44</v>
       </c>
       <c r="T17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -2058,10 +2529,10 @@
         <v>55</v>
       </c>
       <c r="T18" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
         <v>38</v>
       </c>
@@ -2072,7 +2543,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>8</v>
@@ -2087,10 +2558,10 @@
         <v>58</v>
       </c>
       <c r="T19" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="12">
         <v>1</v>
       </c>
@@ -2113,7 +2584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>54</v>
       </c>
@@ -2142,10 +2613,10 @@
         <v>64</v>
       </c>
       <c r="T21" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="4">
         <v>3</v>
       </c>
@@ -2172,7 +2643,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="G23" s="5">
         <v>4</v>
       </c>
@@ -2189,7 +2660,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="G24" s="5">
         <v>5</v>
       </c>
@@ -2203,7 +2674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="G25" s="5">
         <v>6</v>
       </c>
@@ -2217,7 +2688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="G26" s="5">
         <v>7</v>
       </c>
@@ -2231,12 +2702,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>70</v>
       </c>
@@ -2247,12 +2718,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B31" s="9" t="s">
         <v>72</v>
       </c>
@@ -2261,7 +2732,7 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B32" s="9" t="s">
         <v>73</v>
       </c>
@@ -2269,46 +2740,46 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
-      <c r="G32" s="24" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G32" s="22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
-    </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-    </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-    </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-    </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-    </row>
-    <row r="41" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-    </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I42" s="53"/>
-      <c r="J42" s="53"/>
-    </row>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I36" s="47"/>
+      <c r="J36" s="47"/>
+    </row>
+    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I37" s="47"/>
+      <c r="J37" s="47"/>
+    </row>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I38" s="47"/>
+      <c r="J38" s="47"/>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I39" s="47"/>
+      <c r="J39" s="47"/>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I40" s="47"/>
+      <c r="J40" s="47"/>
+    </row>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I41" s="47"/>
+      <c r="J41" s="47"/>
+    </row>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+    </row>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I43" s="47"/>
+      <c r="J43" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2320,17 +2791,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:AJ77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="4" width="8.85546875" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="33" max="33" width="17.7109375" customWidth="1"/>
+    <col min="33" max="33" width="17.6640625" customWidth="1"/>
     <col min="34" max="34" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -2338,24 +2809,24 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="E3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="P4" s="20" t="s">
+      <c r="P4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="T4" s="20" t="s">
+      <c r="T4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="20"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="U4" s="18"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="E5" t="s">
         <v>80</v>
       </c>
@@ -2387,7 +2858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
         <v>81</v>
       </c>
@@ -2413,9 +2884,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>24</v>
@@ -2439,7 +2910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>75</v>
       </c>
@@ -2465,7 +2936,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>98</v>
       </c>
@@ -2482,21 +2953,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C10" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="P10" s="21" t="s">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="C10" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="P10" s="19" t="s">
         <v>83</v>
       </c>
       <c r="T10" s="4" t="s">
@@ -2512,9 +2983,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>84</v>
@@ -2536,7 +3007,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="P12" s="4" t="s">
         <v>67</v>
       </c>
@@ -2545,7 +3016,7 @@
       </c>
       <c r="R12" s="5"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="P13" s="4" t="s">
         <v>85</v>
       </c>
@@ -2554,10 +3025,10 @@
       </c>
       <c r="R13" s="5"/>
       <c r="T13" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="P14" s="4" t="s">
         <v>86</v>
       </c>
@@ -2569,12 +3040,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="T15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
@@ -2586,19 +3057,19 @@
       <c r="X16" s="9"/>
       <c r="Y16" s="9"/>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="T18" s="22" t="s">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.3">
+      <c r="T18" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="U18" s="21"/>
-      <c r="V18" s="21"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
       <c r="W18" s="5"/>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="P19" s="59" t="s">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.3">
+      <c r="P19" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="Q19" s="59"/>
+      <c r="Q19" s="69"/>
       <c r="T19" s="4" t="s">
         <v>9</v>
       </c>
@@ -2612,14 +3083,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:35" x14ac:dyDescent="0.3">
       <c r="P20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="Q20" s="58" t="s">
+      <c r="Q20" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="R20" s="58"/>
+      <c r="R20" s="68"/>
       <c r="T20" s="4" t="s">
         <v>94</v>
       </c>
@@ -2633,14 +3104,14 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.3">
       <c r="P21" s="4">
         <v>1</v>
       </c>
-      <c r="Q21" s="58" t="s">
+      <c r="Q21" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="R21" s="58"/>
+      <c r="R21" s="68"/>
       <c r="T21" s="4" t="s">
         <v>94</v>
       </c>
@@ -2654,14 +3125,14 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.3">
       <c r="P22" s="4">
         <v>2</v>
       </c>
-      <c r="Q22" s="58" t="s">
+      <c r="Q22" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="R22" s="58"/>
+      <c r="R22" s="68"/>
       <c r="T22" s="4" t="s">
         <v>94</v>
       </c>
@@ -2675,36 +3146,36 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.3">
       <c r="P23" s="4">
         <v>3</v>
       </c>
-      <c r="Q23" s="58" t="s">
+      <c r="Q23" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="R23" s="58"/>
+      <c r="R23" s="68"/>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
       <c r="AG23" t="s">
+        <v>212</v>
+      </c>
+      <c r="AH23" t="s">
         <v>213</v>
       </c>
-      <c r="AH23" t="s">
-        <v>214</v>
-      </c>
       <c r="AI23" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.3">
       <c r="P24" s="4">
         <v>4</v>
       </c>
-      <c r="Q24" s="58" t="s">
+      <c r="Q24" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="R24" s="58"/>
+      <c r="R24" s="68"/>
       <c r="T24" s="4" t="s">
         <v>95</v>
       </c>
@@ -2718,63 +3189,63 @@
         <v>105</v>
       </c>
       <c r="AG24" t="s">
+        <v>214</v>
+      </c>
+      <c r="AH24" t="s">
         <v>215</v>
       </c>
-      <c r="AH24" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="T28" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="U28" s="22"/>
-      <c r="X28" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y28" s="22"/>
-      <c r="AA28" s="20" t="s">
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.3">
+      <c r="T28" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="U28" s="20"/>
+      <c r="X28" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y28" s="20"/>
+      <c r="AA28" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="AD28" s="47" t="s">
+      <c r="AD28" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="AF28" s="20" t="s">
+      <c r="AF28" s="18" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="C29" s="21" t="s">
-        <v>122</v>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.3">
+      <c r="C29" s="19" t="s">
+        <v>121</v>
       </c>
       <c r="F29" t="s">
-        <v>213</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="J29" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="J29" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="P29" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="T29" s="40" t="s">
+      <c r="P29" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="T29" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="U29" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="V29" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="X29" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="U29" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="V29" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="X29" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="Y29" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AA29" s="43" t="s">
+      <c r="AA29" s="41" t="s">
         <v>20</v>
       </c>
       <c r="AB29" s="4" t="s">
@@ -2783,127 +3254,127 @@
       <c r="AC29" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AD29" s="45" t="s">
+      <c r="AD29" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="AF29" s="43" t="s">
+      <c r="AF29" s="41" t="s">
         <v>9</v>
       </c>
       <c r="AG29" s="4" t="s">
         <v>21</v>
       </c>
       <c r="AH29" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="AI29" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI29" s="41" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.3">
       <c r="C30" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="E30" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="E30" s="48" t="s">
+      <c r="F30" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I30" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="J30" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="K30" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+      <c r="P30" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q30" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T30" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="U30" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="F30" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="H30" s="6" t="s">
+      <c r="V30" s="27">
+        <v>5</v>
+      </c>
+      <c r="X30" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I30" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="J30" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="K30" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="P30" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q30" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="T30" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="U30" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="V30" s="29">
-        <v>5</v>
-      </c>
-      <c r="X30" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="Y30" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA30" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA30" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="AB30" s="42" t="s">
-        <v>193</v>
+      <c r="AB30" s="40" t="s">
+        <v>192</v>
       </c>
       <c r="AC30" s="4">
         <v>225</v>
       </c>
-      <c r="AD30" s="44" t="s">
+      <c r="AD30" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="AF30" s="44" t="s">
+      <c r="AF30" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="AG30" s="42" t="s">
-        <v>197</v>
+      <c r="AG30" s="40" t="s">
+        <v>196</v>
       </c>
       <c r="AH30" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="AI30" s="44" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="C31" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="AI30" s="42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.3">
+      <c r="C31" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="48">
+      <c r="E31" s="46">
         <v>8</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H31" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="I31" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="J31" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="K31" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="L31" s="37"/>
-      <c r="M31" s="35"/>
+        <v>130</v>
+      </c>
+      <c r="H31" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="I31" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="J31" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="K31" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="L31" s="35"/>
+      <c r="M31" s="33"/>
       <c r="P31" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="4" t="s">
         <v>34</v>
@@ -2911,70 +3382,70 @@
       <c r="R31" s="3">
         <v>7.8</v>
       </c>
-      <c r="T31" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="U31" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="V31" s="29">
+      <c r="T31" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="U31" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="V31" s="27">
         <v>6</v>
       </c>
       <c r="X31" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Y31" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA31" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA31" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="AB31" s="42" t="s">
-        <v>194</v>
+      <c r="AB31" s="40" t="s">
+        <v>193</v>
       </c>
       <c r="AC31" s="4">
         <v>0</v>
       </c>
-      <c r="AD31" s="44" t="s">
+      <c r="AD31" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="AF31" s="44" t="s">
+      <c r="AF31" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="AG31" s="42" t="s">
-        <v>198</v>
+      <c r="AG31" s="40" t="s">
+        <v>197</v>
       </c>
       <c r="AH31" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI31" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI31" s="42" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="C32" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="48" t="s">
+    <row r="32" spans="3:35" x14ac:dyDescent="0.3">
+      <c r="C32" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E32" s="48">
+      <c r="E32" s="46">
         <v>6</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H32" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="I32" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="J32" s="33" t="s">
-        <v>127</v>
+        <v>132</v>
+      </c>
+      <c r="H32" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="I32" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="31" t="s">
+        <v>126</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="4" t="s">
         <v>35</v>
@@ -2982,70 +3453,70 @@
       <c r="R32" s="3">
         <v>8</v>
       </c>
-      <c r="T32" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="U32" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="V32" s="29">
+      <c r="T32" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="U32" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="V32" s="27">
         <v>7</v>
       </c>
       <c r="X32" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Y32" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA32" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB32" s="42" t="s">
-        <v>195</v>
+        <v>135</v>
+      </c>
+      <c r="AA32" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB32" s="40" t="s">
+        <v>194</v>
       </c>
       <c r="AC32" s="4">
         <v>125</v>
       </c>
-      <c r="AD32" s="44" t="s">
+      <c r="AD32" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="AF32" s="44" t="s">
+      <c r="AF32" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="AG32" s="42" t="s">
-        <v>199</v>
+      <c r="AG32" s="40" t="s">
+        <v>198</v>
       </c>
       <c r="AH32" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="AI32" s="44" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="33" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C33" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI32" s="42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C33" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="48">
+      <c r="E33" s="46">
         <v>9</v>
       </c>
       <c r="F33" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H33" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="H33" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="I33" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="J33" s="33" t="s">
-        <v>126</v>
+      <c r="I33" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="J33" s="31" t="s">
+        <v>125</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="4" t="s">
         <v>36</v>
@@ -3053,98 +3524,98 @@
       <c r="R33" s="3">
         <v>9.5</v>
       </c>
-      <c r="T33" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="U33" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="V33" s="29">
+      <c r="T33" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="U33" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="V33" s="27">
         <v>5</v>
       </c>
-      <c r="AA33" s="44" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB33" s="42" t="s">
-        <v>196</v>
+      <c r="AA33" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB33" s="40" t="s">
+        <v>195</v>
       </c>
       <c r="AC33" s="4">
         <v>220</v>
       </c>
-      <c r="AD33" s="44" t="s">
+      <c r="AD33" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="AF33" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="AG33" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH33" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="AF33" s="44" t="s">
-        <v>203</v>
-      </c>
-      <c r="AG33" s="42" t="s">
-        <v>199</v>
-      </c>
-      <c r="AH33" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="AI33" s="44" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C34" s="48" t="s">
+      <c r="AI33" s="42" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C34" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="D34" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="E34" s="48">
+      <c r="E34" s="46">
         <v>7</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P34" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q34" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="Q34" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="R34" s="3">
         <v>2</v>
       </c>
-      <c r="T34" s="38" t="s">
+      <c r="T34" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="U34" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="V34" s="27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C35" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="E35" s="46">
+        <v>7</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="U34" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="V34" s="29">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C35" s="48" t="s">
+      <c r="P35" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q35" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="D35" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="E35" s="48">
-        <v>7</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="P35" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q35" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="R35" s="3">
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="37" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C37" s="34" t="s">
-        <v>152</v>
+    <row r="37" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C37" s="32" t="s">
+        <v>151</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
@@ -3155,8 +3626,8 @@
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
-      <c r="P37" s="34" t="s">
-        <v>212</v>
+      <c r="P37" s="32" t="s">
+        <v>211</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3165,7 +3636,7 @@
       <c r="U37" s="9"/>
       <c r="V37" s="9"/>
       <c r="AA37" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
@@ -3177,583 +3648,583 @@
       <c r="AI37" s="9"/>
       <c r="AJ37" s="9"/>
     </row>
-    <row r="38" spans="3:36" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:36" x14ac:dyDescent="0.3">
       <c r="C38" t="s">
+        <v>137</v>
+      </c>
+      <c r="P38" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C39" t="s">
         <v>138</v>
       </c>
-      <c r="P38" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C39" t="s">
+      <c r="P39" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA39" t="s">
         <v>139</v>
       </c>
-      <c r="P39" t="s">
+    </row>
+    <row r="40" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
+        <v>217</v>
+      </c>
+      <c r="P40" t="s">
         <v>157</v>
       </c>
-      <c r="AA39" t="s">
+      <c r="AA40" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C40" t="s">
-        <v>218</v>
-      </c>
-      <c r="P40" t="s">
-        <v>158</v>
-      </c>
-      <c r="AA40" t="s">
+    <row r="41" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C41" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA41" s="48" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C42" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA42" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB42" s="44"/>
+      <c r="AC42" s="44"/>
+      <c r="AD42" s="44"/>
+      <c r="AE42" s="44"/>
+      <c r="AF42" s="44"/>
+      <c r="AG42" s="44"/>
+      <c r="AH42" s="44"/>
+    </row>
+    <row r="43" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C44" t="s">
+        <v>145</v>
+      </c>
+      <c r="O44" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="T44" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C45" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="41" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C41" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA41" s="50" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C42" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA42" s="46" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB42" s="46"/>
-      <c r="AC42" s="46"/>
-      <c r="AD42" s="46"/>
-      <c r="AE42" s="46"/>
-      <c r="AF42" s="46"/>
-      <c r="AG42" s="46"/>
-      <c r="AH42" s="46"/>
-    </row>
-    <row r="43" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C43" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C44" t="s">
-        <v>146</v>
-      </c>
-      <c r="O44" s="30" t="s">
+      <c r="O45" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="P45" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q45" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="T44" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="45" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C45" t="s">
-        <v>142</v>
-      </c>
-      <c r="O45" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="P45" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q45" s="29" t="s">
+      <c r="R45" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="R45" s="29" t="s">
-        <v>162</v>
-      </c>
       <c r="T45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U45" t="s">
         <v>7</v>
       </c>
       <c r="V45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Y45" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="46" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C46" t="s">
+        <v>142</v>
+      </c>
+      <c r="N46" t="s">
+        <v>175</v>
+      </c>
+      <c r="O46" s="27">
+        <v>1</v>
+      </c>
+      <c r="P46" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="R46" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="T46" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="U46" s="27">
+        <v>1</v>
+      </c>
+      <c r="V46" s="27">
+        <v>8</v>
+      </c>
+      <c r="Y46" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="46" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C46" t="s">
-        <v>143</v>
-      </c>
-      <c r="N46" t="s">
-        <v>176</v>
-      </c>
-      <c r="O46" s="29">
-        <v>1</v>
-      </c>
-      <c r="P46" s="29">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="R46" s="41" t="s">
+      <c r="AE46" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C47" t="s">
+        <v>218</v>
+      </c>
+      <c r="O47" s="27">
+        <v>2</v>
+      </c>
+      <c r="P47" s="27">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="T46" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="U46" s="29">
-        <v>1</v>
-      </c>
-      <c r="V46" s="29">
-        <v>8</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>228</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="47" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C47" t="s">
-        <v>219</v>
-      </c>
-      <c r="O47" s="29">
+      <c r="R47" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="T47" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="U47" s="27">
         <v>2</v>
       </c>
-      <c r="P47" s="29">
-        <v>2</v>
-      </c>
-      <c r="Q47" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="R47" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="T47" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="U47" s="29">
-        <v>2</v>
-      </c>
-      <c r="V47" s="29">
+      <c r="V47" s="27">
         <v>8</v>
       </c>
       <c r="Y47" t="s">
         <v>58</v>
       </c>
       <c r="AF47" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="48" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C48" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="56"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="56"/>
-      <c r="J48" s="56"/>
-      <c r="O48" s="29">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="3:36" x14ac:dyDescent="0.3">
+      <c r="C48" s="65" t="s">
+        <v>220</v>
+      </c>
+      <c r="D48" s="66"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="66"/>
+      <c r="O48" s="27">
         <v>3</v>
       </c>
-      <c r="P48" s="29">
+      <c r="P48" s="27">
         <v>3</v>
       </c>
-      <c r="Q48" s="41" t="s">
+      <c r="Q48" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="R48" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="T48" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="U48" s="27">
+        <v>1</v>
+      </c>
+      <c r="V48" s="27">
+        <v>9</v>
+      </c>
+      <c r="AE48" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF48" s="42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="67" t="s">
+        <v>219</v>
+      </c>
+      <c r="D49" s="67"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="67"/>
+      <c r="G49" s="67"/>
+      <c r="H49" s="67"/>
+      <c r="I49" s="67"/>
+      <c r="J49" s="67"/>
+      <c r="O49" s="27">
+        <v>4</v>
+      </c>
+      <c r="P49" s="27">
+        <v>4</v>
+      </c>
+      <c r="Q49" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="R49" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="T49" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="U49" s="27">
+        <v>1</v>
+      </c>
+      <c r="V49" s="27">
+        <v>9</v>
+      </c>
+      <c r="AE49" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF49" s="42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="O50" s="27">
+        <v>5</v>
+      </c>
+      <c r="P50" s="27">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="R50" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE50" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF50" s="42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="O51" s="27">
+        <v>6</v>
+      </c>
+      <c r="P51" s="27">
+        <v>6</v>
+      </c>
+      <c r="Q51" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="R48" s="41" t="s">
+      <c r="R51" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE51" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF51" s="42" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="C52" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="H52" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="O52" s="27">
+        <v>7</v>
+      </c>
+      <c r="P52" s="27">
+        <v>7</v>
+      </c>
+      <c r="Q52" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="R52" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="AE52" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="AF52" s="42" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="C53" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="E53" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="F53" t="s">
+        <v>128</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I53" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="J53" t="s">
+        <v>121</v>
+      </c>
+      <c r="O53" s="27">
+        <v>8</v>
+      </c>
+      <c r="P53" s="27">
+        <v>8</v>
+      </c>
+      <c r="Q53" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="R53" s="39" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="C54" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" s="46">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>130</v>
+      </c>
+      <c r="H54" s="46"/>
+      <c r="I54" s="46"/>
+      <c r="O54" s="27">
+        <v>9</v>
+      </c>
+      <c r="P54" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="R54" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="T48" s="29" t="s">
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="C55" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="46">
+        <v>6</v>
+      </c>
+      <c r="F55" t="s">
+        <v>130</v>
+      </c>
+      <c r="H55" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="I55" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="J55" t="s">
+        <v>126</v>
+      </c>
+      <c r="N55" t="s">
+        <v>176</v>
+      </c>
+      <c r="O55" s="27">
+        <v>10</v>
+      </c>
+      <c r="P55" s="27">
+        <v>2</v>
+      </c>
+      <c r="Q55" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="R55" s="39" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="C56" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E56" s="46">
+        <v>9</v>
+      </c>
+      <c r="F56" t="s">
+        <v>132</v>
+      </c>
+      <c r="H56" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="I56" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="J56" t="s">
+        <v>125</v>
+      </c>
+      <c r="O56" s="27">
+        <v>11</v>
+      </c>
+      <c r="P56" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="R56" s="39" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="C57" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="D57" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="U48" s="29">
-        <v>1</v>
-      </c>
-      <c r="V48" s="29">
-        <v>9</v>
-      </c>
-      <c r="AE48" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF48" s="44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="3:32" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="57" t="s">
-        <v>220</v>
-      </c>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="57"/>
-      <c r="O49" s="29">
+      <c r="E57" s="46">
+        <v>7</v>
+      </c>
+      <c r="F57" t="s">
+        <v>131</v>
+      </c>
+      <c r="O57" s="27">
+        <v>12</v>
+      </c>
+      <c r="P57" s="27">
         <v>4</v>
       </c>
-      <c r="P49" s="29">
-        <v>4</v>
-      </c>
-      <c r="Q49" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="R49" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="T49" s="29" t="s">
+      <c r="Q57" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="R57" s="39" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="C58" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="D58" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="U49" s="29">
-        <v>1</v>
-      </c>
-      <c r="V49" s="29">
-        <v>9</v>
-      </c>
-      <c r="AE49" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF49" s="44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O50" s="29">
+      <c r="E58" s="46">
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
+        <v>132</v>
+      </c>
+      <c r="O58" s="27">
+        <v>13</v>
+      </c>
+      <c r="P58" s="27">
         <v>5</v>
       </c>
-      <c r="P50" s="29">
-        <v>5</v>
-      </c>
-      <c r="Q50" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="R50" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="AE50" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF50" s="44" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O51" s="29">
+      <c r="Q58" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="R58" s="39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="O59" s="27">
+        <v>14</v>
+      </c>
+      <c r="P59" s="27">
         <v>6</v>
       </c>
-      <c r="P51" s="29">
-        <v>6</v>
-      </c>
-      <c r="Q51" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="R51" s="41" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE51" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="AF51" s="44" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C52" s="21" t="s">
+      <c r="Q59" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="R59" s="39" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="O60" s="27">
+        <v>15</v>
+      </c>
+      <c r="P60" s="27">
+        <v>7</v>
+      </c>
+      <c r="Q60" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="R60" s="39" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.3">
+      <c r="O61" s="27">
+        <v>16</v>
+      </c>
+      <c r="P61" s="27">
+        <v>8</v>
+      </c>
+      <c r="Q61" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="R61" s="39" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="71" spans="17:24" x14ac:dyDescent="0.3">
+      <c r="Q71" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="W71" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="X71" s="20"/>
+    </row>
+    <row r="72" spans="17:24" x14ac:dyDescent="0.3">
+      <c r="Q72" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="H52" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="O52" s="29">
-        <v>7</v>
-      </c>
-      <c r="P52" s="29">
-        <v>7</v>
-      </c>
-      <c r="Q52" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="R52" s="41" t="s">
-        <v>175</v>
-      </c>
-      <c r="AE52" s="44" t="s">
-        <v>192</v>
-      </c>
-      <c r="AF52" s="44" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C53" s="6" t="s">
+      <c r="R72" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D53" s="48" t="s">
+      <c r="S72" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E53" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="T72" t="s">
         <v>129</v>
       </c>
-      <c r="H53" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I53" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="J53" t="s">
-        <v>122</v>
-      </c>
-      <c r="O53" s="29">
-        <v>8</v>
-      </c>
-      <c r="P53" s="29">
-        <v>8</v>
-      </c>
-      <c r="Q53" s="41" t="s">
-        <v>170</v>
-      </c>
-      <c r="R53" s="41" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C54" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="D54" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="E54" s="48">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>131</v>
-      </c>
-      <c r="H54" s="48"/>
-      <c r="I54" s="48"/>
-      <c r="O54" s="29">
-        <v>9</v>
-      </c>
-      <c r="P54" s="29">
-        <v>1</v>
-      </c>
-      <c r="Q54" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="R54" s="41" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C55" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="D55" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="48">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>131</v>
-      </c>
-      <c r="H55" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="I55" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="J55" t="s">
-        <v>127</v>
-      </c>
-      <c r="N55" t="s">
-        <v>177</v>
-      </c>
-      <c r="O55" s="29">
-        <v>10</v>
-      </c>
-      <c r="P55" s="29">
-        <v>2</v>
-      </c>
-      <c r="Q55" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="R55" s="41" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C56" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="E56" s="48">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>133</v>
-      </c>
-      <c r="H56" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="I56" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="J56" t="s">
-        <v>126</v>
-      </c>
-      <c r="O56" s="29">
-        <v>11</v>
-      </c>
-      <c r="P56" s="29">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="R56" s="41" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C57" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="D57" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="E57" s="48">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>132</v>
-      </c>
-      <c r="O57" s="29">
-        <v>12</v>
-      </c>
-      <c r="P57" s="29">
-        <v>4</v>
-      </c>
-      <c r="Q57" s="41" t="s">
-        <v>170</v>
-      </c>
-      <c r="R57" s="41" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C58" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="D58" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="E58" s="48">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>133</v>
-      </c>
-      <c r="O58" s="29">
-        <v>13</v>
-      </c>
-      <c r="P58" s="29">
-        <v>5</v>
-      </c>
-      <c r="Q58" s="41" t="s">
-        <v>182</v>
-      </c>
-      <c r="R58" s="41" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O59" s="29">
-        <v>14</v>
-      </c>
-      <c r="P59" s="29">
-        <v>6</v>
-      </c>
-      <c r="Q59" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="R59" s="41" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O60" s="29">
-        <v>15</v>
-      </c>
-      <c r="P60" s="29">
-        <v>7</v>
-      </c>
-      <c r="Q60" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="R60" s="41" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O61" s="29">
-        <v>16</v>
-      </c>
-      <c r="P61" s="29">
-        <v>8</v>
-      </c>
-      <c r="Q61" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="R61" s="41" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="71" spans="17:24" x14ac:dyDescent="0.25">
-      <c r="Q71" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="W71" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="X71" s="22"/>
-    </row>
-    <row r="72" spans="17:24" x14ac:dyDescent="0.25">
-      <c r="Q72" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="R72" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="T72" t="s">
-        <v>130</v>
-      </c>
       <c r="W72" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="X72" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="17:24" x14ac:dyDescent="0.25">
+    <row r="73" spans="17:24" x14ac:dyDescent="0.3">
       <c r="Q73" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R73" s="4" t="s">
         <v>34</v>
@@ -3762,18 +4233,18 @@
         <v>7.8</v>
       </c>
       <c r="T73" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="W73" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="X73" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="74" spans="17:24" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="74" spans="17:24" x14ac:dyDescent="0.3">
       <c r="Q74" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R74" s="4" t="s">
         <v>35</v>
@@ -3782,18 +4253,18 @@
         <v>8</v>
       </c>
       <c r="T74" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="W74" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="X74" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="75" spans="17:24" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="75" spans="17:24" x14ac:dyDescent="0.3">
       <c r="Q75" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R75" s="4" t="s">
         <v>36</v>
@@ -3802,35 +4273,35 @@
         <v>9.5</v>
       </c>
       <c r="T75" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="W75" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="X75" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="76" spans="17:24" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="76" spans="17:24" x14ac:dyDescent="0.3">
       <c r="Q76" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="R76" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="R76" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="S76" s="3">
         <v>2</v>
       </c>
       <c r="T76" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="77" spans="17:24" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="77" spans="17:24" x14ac:dyDescent="0.3">
       <c r="Q77" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="R77" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="R77" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="S77" s="3">
         <v>4.5999999999999996</v>
@@ -3853,29 +4324,29 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="7" width="21.140625" customWidth="1"/>
+    <col min="1" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="7" width="21.109375" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="13" width="12.7109375" customWidth="1"/>
-    <col min="14" max="14" width="18.28515625" customWidth="1"/>
-    <col min="15" max="22" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="10" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" customWidth="1"/>
+    <col min="15" max="22" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="4" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -3890,7 +4361,7 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="17"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -3905,7 +4376,7 @@
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
     </row>
-    <row r="6" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="17"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -3920,7 +4391,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
       <c r="D7" s="2"/>
@@ -3935,7 +4406,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
       <c r="D8" s="16"/>
@@ -3950,7 +4421,7 @@
       <c r="M8" s="2"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
       <c r="D9" s="2"/>
@@ -3965,7 +4436,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
       <c r="D10" s="2"/>
@@ -3980,7 +4451,7 @@
       <c r="M10" s="2"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="2"/>
@@ -3995,7 +4466,7 @@
       <c r="M11" s="2"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="2"/>
@@ -4010,7 +4481,7 @@
       <c r="M12" s="2"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="2"/>
@@ -4025,7 +4496,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="2"/>
@@ -4040,7 +4511,7 @@
       <c r="M14" s="2"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="2"/>
@@ -4055,7 +4526,7 @@
       <c r="M15" s="2"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="2"/>
@@ -4070,7 +4541,7 @@
       <c r="M16" s="2"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="2"/>
@@ -4085,7 +4556,7 @@
       <c r="M17" s="2"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="2"/>
@@ -4100,7 +4571,7 @@
       <c r="M18" s="2"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="2"/>
@@ -4115,7 +4586,7 @@
       <c r="M19" s="2"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="2"/>
@@ -4130,22 +4601,22 @@
       <c r="M20" s="2"/>
       <c r="N20" s="3"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>109</v>
       </c>
